--- a/data/trans_orig/IP07C08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>31143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46476</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>23035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29314</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43459</t>
+          <t>43467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20607</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63796</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85888</t>
+          <t>87593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74118</t>
+          <t>74040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97498</t>
+          <t>97350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145655</t>
+          <t>145334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176115</t>
+          <t>177575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82262</t>
+          <t>81606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>104086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92158</t>
+          <t>92805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116810</t>
+          <t>116481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182204</t>
+          <t>181896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214303</t>
+          <t>214129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40927</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>32941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44491</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60782</t>
+          <t>60586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126536</t>
+          <t>127464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>105372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132332</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211862</t>
+          <t>211575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249789</t>
+          <t>249427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124980</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151718</t>
+          <t>154353</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134902</t>
+          <t>134809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>162628</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>269841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306873</t>
+          <t>309473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59487</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>84762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>31182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>28820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>32394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48187</t>
+          <t>48131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>70264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93392</t>
+          <t>94622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93175</t>
+          <t>93805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117467</t>
+          <t>117796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170996</t>
+          <t>169360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205843</t>
+          <t>205204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84459</t>
+          <t>84832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107852</t>
+          <t>108435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72809</t>
+          <t>71421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97088</t>
+          <t>95232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163375</t>
+          <t>163685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196522</t>
+          <t>198550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37535</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55500</t>
+          <t>57421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18715</t>
+          <t>19035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50247</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67303</t>
+          <t>67571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54514</t>
+          <t>54313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126732</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134506</t>
+          <t>134379</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164330</t>
+          <t>163929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269592</t>
+          <t>267706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310401</t>
+          <t>310286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154976</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>140199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245461</t>
+          <t>246755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>285863</t>
+          <t>288349</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>54614</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>55041</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79786</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>24549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41798</t>
+          <t>41895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109710</t>
+          <t>109795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134701</t>
+          <t>134382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105259</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130340</t>
+          <t>130015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222247</t>
+          <t>220974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260891</t>
+          <t>260011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79407</t>
+          <t>79791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105368</t>
+          <t>105321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>78026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103772</t>
+          <t>104294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165226</t>
+          <t>165198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202801</t>
+          <t>202296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37106</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>60585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45605</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55453</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77499</t>
+          <t>76832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95839</t>
+          <t>96570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>19999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33803</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54609</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153574</t>
+          <t>154255</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185605</t>
+          <t>185656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159736</t>
+          <t>160037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>191912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324735</t>
+          <t>323165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>367413</t>
+          <t>367519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>151444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>114035</t>
+          <t>111644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145438</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>244634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>284899</t>
+          <t>285625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84399</t>
+          <t>85186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as, percibida por el/la menor en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17820</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13009</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22851</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>20316</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15170</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25594</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15087</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25983</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17820</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12929</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23039</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17919</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13178</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23308</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18672</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13429</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23731</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13116</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23796</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17919</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13141</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23035</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43467</t>
+          <t>44129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7485</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12194</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6373</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3261</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10638</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3064</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10433</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7485</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12159</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3286</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3664</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84836</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73077</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95961</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>75614</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65408</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87593</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>65881</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>86333</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84836</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>74040</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>97350</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145334</t>
+          <t>145655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177575</t>
+          <t>177199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105058</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>94281</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>117184</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>93621</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81606</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>104086</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>82645</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>104415</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>49,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105058</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>92805</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>116481</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>48,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181896</t>
+          <t>182514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214129</t>
+          <t>213546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23518</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16588</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31889</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24631</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11940</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24694</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,37%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23518</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16881</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31121</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>53362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4686</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2645</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6536</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4682</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3724</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4789</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>216595</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>216595</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>216595</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>216595</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>216595</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>216595</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15067</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9552</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20548</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17308</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12193</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22938</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12400</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23066</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,3%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>15067</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9994</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20459</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25539</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19401</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31094</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>27020</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21158</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>32941</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20872</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32993</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>50,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>25539</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19756</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31338</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60586</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12441</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9264</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5517</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14848</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>14510</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>17,29%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11192</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1401</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4768</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5593</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4779</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53593</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53593</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53593</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>117723</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>104623</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>131520</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,12%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>113237</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>99120</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>127464</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>100476</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>127149</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>39,05%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>34,18%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>117723</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>105372</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>132408</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211575</t>
+          <t>210460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249427</t>
+          <t>250800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>148516</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>134540</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>161155</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>48,09%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>52,18%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>139312</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>125719</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>154353</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>124913</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>153007</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>48,04%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>148516</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>134809</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>162628</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269841</t>
+          <t>268018</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>309473</t>
+          <t>309440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>38036</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>28963</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>46817</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>33483</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>25664</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>43464</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>25569</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>43552</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>11,55%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>38036</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>29316</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>47211</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>58994</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84762</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -3112,67 +3112,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7213</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7069</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4824</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>308859</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>308859</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>308859</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>289992</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>289992</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>289992</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>308859</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>308859</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>308859</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as, percibida por el/la menor en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18959</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13571</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24475</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25277</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19203</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31182</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31456</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>18959</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13628</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24598</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>41,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>35266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52456</t>
+          <t>52797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17663</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12350</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23341</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22780</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17323</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28820</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16668</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28899</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17663</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12504</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23284</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>32731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12398</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2801</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6407</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6471</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,43%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7309</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3913</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12160</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1231</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3902</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3781</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4371</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4109</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>105890</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91741</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>117446</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>81633</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>70264</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>94622</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>70050</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>93257</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>105890</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93805</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>117796</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169360</t>
+          <t>170413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205204</t>
+          <t>203197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84157</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72783</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>97237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96324</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84832</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108435</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>84422</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>107273</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,38%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84157</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71421</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163685</t>
+          <t>164465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198550</t>
+          <t>196954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28749</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21520</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37633</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16576</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11129</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23462</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11119</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23661</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28749</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20959</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37133</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36200</t>
+          <t>36264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57421</t>
+          <t>56356</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3781</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7719</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3090</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6938</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3781</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8301</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2188</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6551</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1465</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5194</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2188</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6586</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199087</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199087</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199087</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24541</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18535</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31155</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33977</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27356</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40095</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>27718</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39769</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24541</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19035</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31066</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49876</t>
+          <t>49128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67571</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17489</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30079</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21202</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14947</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27518</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15498</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>27941</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23820</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18324</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30407</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>36219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54313</t>
+          <t>53580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7166</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3573</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7566</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7731</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,95%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7166</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3730</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12280</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3412</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3079</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5502,102 +5502,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3843</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3181</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60086</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60086</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60086</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>149390</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>133464</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>162119</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>45,81%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>140887</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>125399</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>155208</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>126600</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>154887</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>45,33%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>49,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>149390</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>134379</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>163929</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>45,81%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267706</t>
+          <t>272032</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310286</t>
+          <t>312876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>125640</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>111819</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>141112</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>34,29%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>140305</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>126044</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>156359</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>126617</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>155094</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>45,14%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>125640</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>112337</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>140199</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>38,53%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246755</t>
+          <t>245713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288349</t>
+          <t>285354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>33787</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>53972</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>22949</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17035</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>31349</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>16329</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>30532</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>33139</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>54614</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55041</t>
+          <t>54032</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79282</t>
+          <t>80142</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5012</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3698</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7363</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5012</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9132</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6184,67 +6184,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7297</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>2959</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6637</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7206</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>7036</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>310798</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as, percibida por el/la menor en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9851</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15032</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7996</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12461</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12534</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9851</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5867</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14651</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16996</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12047</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22085</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18440</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13484</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22737</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13467</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22463</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>60,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16996</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11567</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21928</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41895</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11522</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,03%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4170</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1593</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8163</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1863</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6807</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3644</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11272</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>18,92%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -6979,92 +6979,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2321</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2321</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6321</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2321</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35976</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35976</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35976</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35976</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35976</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117708</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>105133</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>130826</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>122823</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>109795</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>134382</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>108956</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>135454</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>50,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>117708</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>104050</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>130015</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220974</t>
+          <t>221197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260011</t>
+          <t>257554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>90638</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>77827</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101842</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>92270</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>79791</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105321</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79635</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105258</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>90638</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>78026</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104294</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165198</t>
+          <t>164507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202296</t>
+          <t>201346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22620</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15457</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31020</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25505</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19392</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34012</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18367</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>34254</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,45%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22620</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15936</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31473</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -7661,74 +7661,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4165</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8143</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1516</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4711</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4165</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8940</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5684</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5061</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>236411</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>236411</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>236411</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>236411</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>236411</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>236411</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48804</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41815</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,38%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38362</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31084</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45199</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31453</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>45768</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>54,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>48804</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>42079</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>55435</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>77012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96570</t>
+          <t>96297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19083</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13046</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>26274</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19999</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33483</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19756</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33230</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19083</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>13728</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>25573</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54272</t>
+          <t>55424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6175</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11108</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5141</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9891</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9967</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,3%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>6175</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2929</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11243</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -8348,102 +8348,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4845</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1578</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4120</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5867</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1578</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5352</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3134</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2779</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>70463</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>70463</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>70463</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>176363</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>160779</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>192521</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>46,22%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>169182</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>154255</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>185656</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>153984</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>183308</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>49,03%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>176363</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>160037</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>191912</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323165</t>
+          <t>326223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>367519</t>
+          <t>368835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>126718</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>112215</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>142770</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,42%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,04%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>136984</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>121276</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>151444</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>122664</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>152548</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>39,7%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,15%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,89%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126718</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>111644</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>142613</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244634</t>
+          <t>242256</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>285625</t>
+          <t>284457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -8917,67 +8917,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>35603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>27216</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>45636</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>34816</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>26417</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>44878</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>26593</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>45586</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>35603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>27140</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>46065</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58354</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85186</t>
+          <t>84140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>13704</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2202</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5670</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>7378</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3868</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>13442</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -9143,67 +9143,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4962</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5087</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>347889</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>347889</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>347889</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>345068</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>345068</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>345068</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>347889</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>347889</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>347889</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
